--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3792,7 +3792,7 @@
         <v>111608615</v>
       </c>
       <c r="B27" t="n">
-        <v>55984</v>
+        <v>55985</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3792,7 +3792,7 @@
         <v>111608615</v>
       </c>
       <c r="B27" t="n">
-        <v>55985</v>
+        <v>55988</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3792,7 +3792,7 @@
         <v>111608615</v>
       </c>
       <c r="B27" t="n">
-        <v>55988</v>
+        <v>55992</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3792,7 +3792,7 @@
         <v>111608615</v>
       </c>
       <c r="B27" t="n">
-        <v>55992</v>
+        <v>55999</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3792,7 +3792,7 @@
         <v>111608615</v>
       </c>
       <c r="B27" t="n">
-        <v>55999</v>
+        <v>56001</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3913,6 +3913,200 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129036032</v>
+      </c>
+      <c r="B28" t="n">
+        <v>90415</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>655</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Oxtungssvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fistulina hepatica</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaeff.) With., nom sanct.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Långöarna, Långöarna, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>340397</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6522622</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson, Samuel Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129036072</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91073</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>937</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vit vedfingersvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lentaria epichnoa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Corner</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Myrön, Myrön, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>340354</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6522748</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson, Samuel Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3918,7 +3918,7 @@
         <v>129036032</v>
       </c>
       <c r="B28" t="n">
-        <v>90422</v>
+        <v>90425</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129036072</v>
       </c>
       <c r="B29" t="n">
-        <v>91080</v>
+        <v>91083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3918,7 +3918,7 @@
         <v>129036032</v>
       </c>
       <c r="B28" t="n">
-        <v>90425</v>
+        <v>90428</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129036072</v>
       </c>
       <c r="B29" t="n">
-        <v>91083</v>
+        <v>91086</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3918,7 +3918,7 @@
         <v>129036032</v>
       </c>
       <c r="B28" t="n">
-        <v>90428</v>
+        <v>90432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129036072</v>
       </c>
       <c r="B29" t="n">
-        <v>91086</v>
+        <v>91090</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3918,7 +3918,7 @@
         <v>129036032</v>
       </c>
       <c r="B28" t="n">
-        <v>90432</v>
+        <v>90439</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129036072</v>
       </c>
       <c r="B29" t="n">
-        <v>91090</v>
+        <v>91097</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3918,7 +3918,7 @@
         <v>129036032</v>
       </c>
       <c r="B28" t="n">
-        <v>90439</v>
+        <v>90441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129036072</v>
       </c>
       <c r="B29" t="n">
-        <v>91097</v>
+        <v>91099</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3918,7 +3918,7 @@
         <v>129036032</v>
       </c>
       <c r="B28" t="n">
-        <v>90441</v>
+        <v>90442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129036072</v>
       </c>
       <c r="B29" t="n">
-        <v>91099</v>
+        <v>91100</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4107,6 +4107,215 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129407780</v>
+      </c>
+      <c r="B30" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Långöarna, Långöarna, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>340409</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6522529</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129407004</v>
+      </c>
+      <c r="B31" t="n">
+        <v>91835</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>73</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Veckticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fomitopsis pulvinascens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Långöarna, Långöarna, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>340398</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6522653</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson, Samuel Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3918,7 +3918,7 @@
         <v>129036032</v>
       </c>
       <c r="B28" t="n">
-        <v>90442</v>
+        <v>90445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129036072</v>
       </c>
       <c r="B29" t="n">
-        <v>91100</v>
+        <v>91103</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129407004</v>
       </c>
       <c r="B31" t="n">
-        <v>91835</v>
+        <v>91838</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3918,7 +3918,7 @@
         <v>129036032</v>
       </c>
       <c r="B28" t="n">
-        <v>90445</v>
+        <v>90447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129036072</v>
       </c>
       <c r="B29" t="n">
-        <v>91103</v>
+        <v>91105</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129407004</v>
       </c>
       <c r="B31" t="n">
-        <v>91838</v>
+        <v>91840</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3918,7 +3918,7 @@
         <v>129036032</v>
       </c>
       <c r="B28" t="n">
-        <v>90447</v>
+        <v>90451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129036072</v>
       </c>
       <c r="B29" t="n">
-        <v>91105</v>
+        <v>91109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129407004</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3918,7 +3918,7 @@
         <v>129036032</v>
       </c>
       <c r="B28" t="n">
-        <v>90451</v>
+        <v>90452</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129036072</v>
       </c>
       <c r="B29" t="n">
-        <v>91109</v>
+        <v>91110</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129407004</v>
       </c>
       <c r="B31" t="n">
-        <v>91844</v>
+        <v>91845</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -3918,7 +3918,7 @@
         <v>129036032</v>
       </c>
       <c r="B28" t="n">
-        <v>90452</v>
+        <v>90455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>129036072</v>
       </c>
       <c r="B29" t="n">
-        <v>91110</v>
+        <v>91113</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>129407004</v>
       </c>
       <c r="B31" t="n">
-        <v>91845</v>
+        <v>91848</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -4209,7 +4209,7 @@
         <v>129407004</v>
       </c>
       <c r="B31" t="n">
-        <v>91848</v>
+        <v>91876</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -4209,7 +4209,7 @@
         <v>129407004</v>
       </c>
       <c r="B31" t="n">
-        <v>91876</v>
+        <v>91882</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -4209,7 +4209,7 @@
         <v>129407004</v>
       </c>
       <c r="B31" t="n">
-        <v>91882</v>
+        <v>91883</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -4209,7 +4209,7 @@
         <v>129407004</v>
       </c>
       <c r="B31" t="n">
-        <v>91883</v>
+        <v>91888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -4209,7 +4209,7 @@
         <v>129407004</v>
       </c>
       <c r="B31" t="n">
-        <v>91888</v>
+        <v>91892</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -4209,7 +4209,7 @@
         <v>129407004</v>
       </c>
       <c r="B31" t="n">
-        <v>91892</v>
+        <v>91894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111608642</v>
+        <v>111608634</v>
       </c>
       <c r="B2" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>340443.4752483592</v>
+        <v>340401</v>
       </c>
       <c r="R2" t="n">
-        <v>6522474.792561513</v>
+        <v>6522686</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På murken tallåga.</t>
+          <t>På murken granlåga.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,54 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111608660</v>
+        <v>111608642</v>
       </c>
       <c r="B3" t="n">
-        <v>94777</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2326</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>340423.2444728116</v>
+        <v>340444</v>
       </c>
       <c r="R3" t="n">
-        <v>6522437.771849016</v>
+        <v>6522475</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,44 +850,28 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bra signalart med riklig förekomst.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Mindre sumpskogsparti i naturskog.</t>
+          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På fuktiga lågor och rötter.</t>
+          <t>På murken tallåga.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -929,57 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111608670</v>
+        <v>129407004</v>
       </c>
       <c r="B4" t="n">
-        <v>94777</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2326</v>
+        <v>73</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långöarna i Marsjön, Dls</t>
+          <t>Långöarna, Långöarna, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>340419.1010813658</v>
+        <v>340398</v>
       </c>
       <c r="R4" t="n">
-        <v>6522425.497051922</v>
+        <v>6522653</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,27 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bra signalart med riklig förekomst.</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,66 +968,65 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Mindre sumpskogsparti i naturskog.</t>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På fuktiga lågor och rötter.</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Christine Bryngelsson, Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111608686</v>
+        <v>111608693</v>
       </c>
       <c r="B5" t="n">
-        <v>93067</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stubbtrådmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Fuscocephaloziopsis catenulata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1101,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>340270.8787794594</v>
+        <v>340260</v>
       </c>
       <c r="R5" t="n">
-        <v>6522383.909970115</v>
+        <v>6522363</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1134,21 +1069,11 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1161,6 +1086,11 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>På murken låga.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,57 +1108,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111608671</v>
+        <v>129036032</v>
       </c>
       <c r="B6" t="n">
-        <v>94777</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90801</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2326</v>
+        <v>655</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Oxtungssvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Fistulina hepatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Schaeff.) With., nom sanct.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långöarna i Marsjön, Dls</t>
+          <t>Långöarna, Långöarna, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>340412.1451181638</v>
+        <v>340397</v>
       </c>
       <c r="R6" t="n">
-        <v>6522420.598461484</v>
+        <v>6522622</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,27 +1173,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bra signalart med riklig förekomst.</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,79 +1187,67 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Mindre sumpskogsparti i naturskog.</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>På fuktiga lågor och rötter.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Christine Bryngelsson, Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111608680</v>
+        <v>111608658</v>
       </c>
       <c r="B7" t="n">
-        <v>93388</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Platt spretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Herzogiella turfacea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Lindb.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>340373.8683749607</v>
+        <v>340434</v>
       </c>
       <c r="R7" t="n">
-        <v>6522386.915489013</v>
+        <v>6522459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,19 +1277,14 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Arten ingår i EU:s Art- och habitatdirektiv. Endast lite av arten påträffades, men mer kan ha dolt sig bland Herzogiella seligeri som också fanns på platsen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,12 +1293,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
+          <t>Mindre sumpskogsparti i naturskog.</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>På humus i kanten på blöthål.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1427,50 +1322,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111608650</v>
+        <v>129036072</v>
       </c>
       <c r="B8" t="n">
-        <v>93067</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2810</v>
+        <v>937</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vit vedfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lentaria epichnoa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Fr.) Corner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långöarna i Marsjön, Dls</t>
+          <t>Myrön, Myrön, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>340427.7511838276</v>
+        <v>340354</v>
       </c>
       <c r="R8" t="n">
-        <v>6522458.847377112</v>
+        <v>6522748</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1497,22 +1387,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,80 +1403,61 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Mindre sumpskogsparti i naturskog.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Christine Bryngelsson, Samuel Sjöberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111608617</v>
+        <v>111608635</v>
       </c>
       <c r="B9" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>340280.9227169114</v>
+        <v>340401</v>
       </c>
       <c r="R9" t="n">
-        <v>6522601.813476441</v>
+        <v>6522686</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1626,21 +1487,11 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1653,6 +1504,11 @@
       <c r="AI9" t="inlineStr">
         <is>
           <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>På två murkna granlågor.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1670,37 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111608657</v>
+        <v>111608638</v>
       </c>
       <c r="B10" t="n">
-        <v>93171</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1710,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>340435.0333367331</v>
+        <v>340454</v>
       </c>
       <c r="R10" t="n">
-        <v>6522459.065310571</v>
+        <v>6522639</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1743,21 +1594,11 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1769,12 +1610,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Mindre sumpskogsparti i naturskog.</t>
+          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>På fuktiga lågor och rötter.</t>
+          <t>På grov granlåga.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1792,37 +1633,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111608677</v>
+        <v>111608641</v>
       </c>
       <c r="B11" t="n">
-        <v>93172</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2819</v>
+        <v>990</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trind spretmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Herzogiella striatella</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1832,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>340402.3979863143</v>
+        <v>340444</v>
       </c>
       <c r="R11" t="n">
-        <v>6522423.593818751</v>
+        <v>6522475</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1865,21 +1701,11 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1891,12 +1717,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Mindre sumpskogsparti i naturskog.</t>
+          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>På basen av stubbe.</t>
+          <t>På murken tallåga.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1914,54 +1740,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111608658</v>
+        <v>111608673</v>
       </c>
       <c r="B12" t="n">
-        <v>93173</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>771</v>
+        <v>990</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Platt spretmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella turfacea</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lindb.) Z.Iwats.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>340435.0333367331</v>
+        <v>340402</v>
       </c>
       <c r="R12" t="n">
-        <v>6522459.065310571</v>
+        <v>6522423</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1991,33 +1808,17 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Arten ingår i EU:s Art- och habitatdirektiv. Endast lite av arten påträffades, men mer kan ha dolt sig bland Herzogiella seligeri som också fanns på platsen.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2028,7 +1829,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På humus i kanten på blöthål.</t>
+          <t>På murken låga.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2046,15 +1847,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111608640</v>
+        <v>111608680</v>
       </c>
       <c r="B13" t="n">
-        <v>95211</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2606</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2086,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>340434.72274023</v>
+        <v>340373</v>
       </c>
       <c r="R13" t="n">
-        <v>6522476.709604376</v>
+        <v>6522387</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2119,21 +1915,11 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2146,11 +1932,6 @@
       <c r="AI13" t="inlineStr">
         <is>
           <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>På avbruten asp.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2171,12 +1952,7 @@
         <v>111608655</v>
       </c>
       <c r="B14" t="n">
-        <v>94777</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2212,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>340425.1423387461</v>
+        <v>340425</v>
       </c>
       <c r="R14" t="n">
-        <v>6522445.990713931</v>
+        <v>6522445</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2245,19 +2021,9 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2300,15 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111608678</v>
+        <v>111608660</v>
       </c>
       <c r="B15" t="n">
-        <v>94777</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2344,10 +2105,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>340402.3979863143</v>
+        <v>340423</v>
       </c>
       <c r="R15" t="n">
-        <v>6522423.593818751</v>
+        <v>6522438</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2377,19 +2138,9 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2432,50 +2183,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111608673</v>
+        <v>111608668</v>
       </c>
       <c r="B16" t="n">
-        <v>94450</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>990</v>
+        <v>2326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>340402.3979863143</v>
+        <v>340418</v>
       </c>
       <c r="R16" t="n">
-        <v>6522423.593818751</v>
+        <v>6522433</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2505,19 +2255,14 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bra signalart med riklig förekomst.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2526,17 +2271,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>Mindre sumpskogsparti i naturskog.</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>På murken låga.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2554,15 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111608668</v>
+        <v>111608670</v>
       </c>
       <c r="B17" t="n">
-        <v>94777</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2598,10 +2334,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>340417.887177369</v>
+        <v>340419</v>
       </c>
       <c r="R17" t="n">
-        <v>6522433.844418664</v>
+        <v>6522425</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2631,19 +2367,9 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2664,6 +2390,11 @@
       <c r="AI17" t="inlineStr">
         <is>
           <t>Mindre sumpskogsparti i naturskog.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>På fuktiga lågor och rötter.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2681,50 +2412,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111608638</v>
+        <v>111608671</v>
       </c>
       <c r="B18" t="n">
-        <v>94450</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>990</v>
+        <v>2326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>340453.3614079838</v>
+        <v>340413</v>
       </c>
       <c r="R18" t="n">
-        <v>6522638.768179116</v>
+        <v>6522421</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2754,19 +2484,14 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bra signalart med riklig förekomst.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2775,17 +2500,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
+          <t>Mindre sumpskogsparti i naturskog.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>På grov granlåga.</t>
+          <t>På fuktiga lågor och rötter.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2803,50 +2529,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111608635</v>
+        <v>111608672</v>
       </c>
       <c r="B19" t="n">
-        <v>94450</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>990</v>
+        <v>2326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>340401.3079049361</v>
+        <v>340406</v>
       </c>
       <c r="R19" t="n">
-        <v>6522686.549517915</v>
+        <v>6522425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2876,19 +2601,14 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bra signalart med riklig förekomst.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2897,17 +2617,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
+          <t>Mindre sumpskogsparti i naturskog.</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>På två murkna granlågor.</t>
+          <t>På fuktiga lågor och rötter.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2925,50 +2646,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111608641</v>
+        <v>111608678</v>
       </c>
       <c r="B20" t="n">
-        <v>94450</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>990</v>
+        <v>2326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vanlig rörsvepemossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Liochlaena lanceolata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>Nees</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>340443.4752483592</v>
+        <v>340402</v>
       </c>
       <c r="R20" t="n">
-        <v>6522474.792561513</v>
+        <v>6522423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2998,19 +2718,14 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bra signalart med riklig förekomst.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3019,17 +2734,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
+          <t>Mindre sumpskogsparti i naturskog.</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>På murken tallåga.</t>
+          <t>På fuktiga lågor och rötter.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3047,15 +2763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111608648</v>
+        <v>111608640</v>
       </c>
       <c r="B21" t="n">
-        <v>98535</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3063,21 +2774,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>2606</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3087,10 +2798,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>340427.7511838276</v>
+        <v>340435</v>
       </c>
       <c r="R21" t="n">
-        <v>6522458.847377112</v>
+        <v>6522477</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3120,21 +2831,11 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3146,7 +2847,12 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Mindre sumpskogsparti i naturskog.</t>
+          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>På avbruten asp.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3164,15 +2870,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111608672</v>
+        <v>111608625</v>
       </c>
       <c r="B22" t="n">
-        <v>94777</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3180,38 +2881,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2326</v>
+        <v>2667</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig rörsvepemossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Liochlaena lanceolata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nees</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>340406.0711620924</v>
+        <v>340256</v>
       </c>
       <c r="R22" t="n">
-        <v>6522424.479307228</v>
+        <v>6522743</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3241,44 +2938,28 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bra signalart med riklig förekomst.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>Mindre sumpskogsparti i naturskog.</t>
+          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>På fuktiga lågor och rötter.</t>
+          <t>På sten, lodyta.</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3296,37 +2977,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111608693</v>
+        <v>111608621</v>
       </c>
       <c r="B23" t="n">
-        <v>94145</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>291</v>
+        <v>2810</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stubbtrådmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis catenulata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3336,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>340260.1260604261</v>
+        <v>340256</v>
       </c>
       <c r="R23" t="n">
-        <v>6522362.573664523</v>
+        <v>6522743</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3369,21 +3045,11 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3396,11 +3062,6 @@
       <c r="AI23" t="inlineStr">
         <is>
           <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>På murken låga.</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3418,37 +3079,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111608634</v>
+        <v>111608650</v>
       </c>
       <c r="B24" t="n">
-        <v>94134</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>2810</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3458,10 +3114,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>340401.3079049361</v>
+        <v>340428</v>
       </c>
       <c r="R24" t="n">
-        <v>6522686.549517915</v>
+        <v>6522459</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3491,21 +3147,11 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3517,12 +3163,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>På murken granlåga.</t>
+          <t>Mindre sumpskogsparti i naturskog.</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3543,12 +3184,7 @@
         <v>111608661</v>
       </c>
       <c r="B25" t="n">
-        <v>93067</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3580,10 +3216,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>340417.887177369</v>
+        <v>340418</v>
       </c>
       <c r="R25" t="n">
-        <v>6522433.844418664</v>
+        <v>6522433</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3613,19 +3249,9 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-08-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3657,15 +3283,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111608633</v>
+        <v>111608686</v>
       </c>
       <c r="B26" t="n">
-        <v>78536</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3673,21 +3294,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>2810</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3697,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>340401.3079049361</v>
+        <v>340271</v>
       </c>
       <c r="R26" t="n">
-        <v>6522686.549517915</v>
+        <v>6522384</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3730,21 +3351,11 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3757,21 +3368,6 @@
       <c r="AI26" t="inlineStr">
         <is>
           <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>På asp. # Populus tremula</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3789,15 +3385,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111608615</v>
+        <v>111608657</v>
       </c>
       <c r="B27" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3805,48 +3396,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>340327</v>
+        <v>340434</v>
       </c>
       <c r="R27" t="n">
-        <v>6522423</v>
+        <v>6522459</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3881,11 +3458,6 @@
           <t>2023-08-19</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>En tupp som gick på backen.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3897,7 +3469,12 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
+          <t>Mindre sumpskogsparti i naturskog.</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>På fuktiga lågor och rötter.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3915,48 +3492,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129036032</v>
+        <v>111608677</v>
       </c>
       <c r="B28" t="n">
-        <v>90455</v>
+        <v>96459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>655</v>
+        <v>2819</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oxtungssvamp</t>
+          <t>Trind spretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fistulina hepatica</t>
+          <t>Herzogiella striatella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schaeff.) With., nom sanct.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långöarna, Långöarna, Dls</t>
+          <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>340397</v>
+        <v>340402</v>
       </c>
       <c r="R28" t="n">
-        <v>6522622</v>
+        <v>6522423</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3980,12 +3557,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3996,61 +3573,85 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Mindre sumpskogsparti i naturskog.</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>På basen av stubbe.</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Samuel Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129036072</v>
+        <v>111608615</v>
       </c>
       <c r="B29" t="n">
-        <v>91113</v>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>937</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vit vedfingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lentaria epichnoa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Corner</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Myrön, Myrön, Dls</t>
+          <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>340354</v>
+        <v>340327</v>
       </c>
       <c r="R29" t="n">
-        <v>6522748</v>
+        <v>6522423</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4077,12 +3678,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>En tupp som gick på backen.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4093,26 +3699,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson, Samuel Sjöberg</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129407780</v>
+        <v>111608614</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>57144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4120,34 +3731,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>102613</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långöarna, Långöarna, Dls</t>
+          <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>340409</v>
+        <v>340300</v>
       </c>
       <c r="R30" t="n">
-        <v>6522529</v>
+        <v>6522551</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4174,12 +3789,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spillning påträffad.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4190,26 +3810,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Christine Bryngelsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129407004</v>
+        <v>111608617</v>
       </c>
       <c r="B31" t="n">
-        <v>91894</v>
+        <v>58114</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4217,37 +3842,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>73</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långöarna, Långöarna, Dls</t>
+          <t>Långöarna i Marsjön, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>340398</v>
+        <v>340281</v>
       </c>
       <c r="R31" t="n">
-        <v>6522653</v>
+        <v>6522602</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4271,12 +3905,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4288,33 +3922,339 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129407780</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långöarna, Långöarna, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>340409</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6522529</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
           <t>Christine Bryngelsson</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Christine Bryngelsson, Samuel Sjöberg</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Christine Bryngelsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>111608648</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långöarna i Marsjön, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>340428</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6522459</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Mindre sumpskogsparti i naturskog.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>111608633</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långöarna i Marsjön, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>340401</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6522686</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bäcke</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Naturskogsartat område, gran och tall med inslag av asp och björk + lite ek och rönn. Ställvis mycket lågor.</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>På asp. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34258-2023 artfynd.xlsx
+++ b/artfynd/A 34258-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608634</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608642</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129407004</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608693</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129036032</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608658</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129036072</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608635</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608638</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1737,6 +1787,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608641</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1844,6 +1899,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608673</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608680</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608655</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2180,6 +2250,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608660</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608668</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2409,6 +2489,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608670</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2526,6 +2611,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608671</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2643,6 +2733,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608672</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2760,6 +2855,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608678</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2867,6 +2967,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608640</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2974,6 +3079,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608625</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3076,6 +3186,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608621</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3178,6 +3293,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608650</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3280,6 +3400,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608661</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3382,6 +3507,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608686</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3489,6 +3619,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608657</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3596,6 +3731,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608677</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3717,6 +3857,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608615</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3828,6 +3973,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608614</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3939,6 +4089,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608617</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4036,6 +4191,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129407780</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4138,6 +4298,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608648</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4255,8 +4420,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111608633</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>